--- a/docs/02_ロール一覧.xlsx
+++ b/docs/02_ロール一覧.xlsx
@@ -973,7 +973,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>inventory/host_vars/Ansible-TEST-FS.yml</t>
+          <t>inventory/host_vars/Ansible-TEST-FS/main.yml</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1074,6 +1074,97 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>### 実機検証で判明した「毎回 changed になる」タスク（2026-09-18）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>状態が変わっているのではなく、変更の有無を判定していないために毎回 changed と</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>報告されるタスクが 3 件あります。実害はありませんが、繰り返し実行したときに</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>changed=0 にはなりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>| Playbook | タスク | 理由 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>| --- | --- | --- |</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>| 01_os_initial.yml | post_tasks の再起動 | 条件なしで win_reboot を実行している |</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>| 02_domain.yml（win_ntp） | 外部 NTP サーバとの手動同期設定 | w32tm /config は設定が同じでも「正常に完了」を返すため changed_when が毎回成立する |</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>| 02_domain.yml（win_ntp） | Windows Time サービスの再起動 | state: restarted は無条件に changed |</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>実測値: 01_os_initial.yml の 2 回目が ok=52 changed=1、</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>02_domain.yml は 2 回とも ok=14 changed=2 failed=0 skipped=10。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>改善する場合は、w32tm /query /configuration で現在のピア一覧を読み、</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>設計値と異なるときだけ /config と再起動を実行する形にします。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/02_ロール一覧.xlsx
+++ b/docs/02_ロール一覧.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -503,306 +503,328 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>win_disk</t>
+          <t>win_standard</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1.4 ドライブ構成 / 8.ﾃﾞｨｽｸの管理</t>
+          <t>（全般）</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Azure 一時ディスクの D: → Z: 退避、データディスクの初期化(MBR)・パーティション作成・NTFS フォーマット</t>
+          <t>JBCC 標準の既定値だけを持つロール（タスクなし）。 他の全ロールが meta/main.yml の依存で読み込む。複数ロールから参照される値（win_verify の突合せで使う値を含む）をここに集約する</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>data_disks / azure_move_temp_drive / azure_temp_drive_letter</t>
+          <t>enable_domain_join / ad_domain_name / os_timezone / os_locale / disable_ipv6 / enable_rdp / rdp_require_nla / disable_defender_by_policy / disable_uac / disable_auto_update_policy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>win_network</t>
+          <t>win_disk</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1.5 ネットワーク設定 / 10.ﾈｯﾄﾜｰｸ設定 / 11.hosts</t>
+          <t>1.4 ドライブ構成 / 8.ﾃﾞｨｽｸの管理</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>IPv6 無効化（レジストリ DisabledComponents=0xFF ＋ NIC バインド解除）、hosts エントリ登録、IP/DNS 現況の記録</t>
+          <t>Azure 一時ディスクの D: → Z: 退避、データディスクの初期化(MBR)・パーティション作成・NTFS フォーマット</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>disable_ipv6 / hosts_entries</t>
+          <t>data_disks / azure_move_temp_drive / azure_temp_drive_letter</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>win_os_basic</t>
+          <t>win_network</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>1.6 言語設定 / 3.ｻｰﾊﾞｰﾏﾈｰｼﾞｬｰ / 4.Windowsﾛｸﾞ(20480KB×3) / 5.ｼｽﾃﾑのﾌﾟﾛﾊﾟﾃｨ</t>
+          <t>1.5 ネットワーク設定 / 10.ﾈｯﾄﾜｰｸ設定 / 11.hosts</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>コンピュータ名、タイムゾーン、日本語ロケール、IE ESC 無効化、テレメトリ オフ、イベントログ最大サイズ、ページングファイル</t>
+          <t>IPv6 無効化（レジストリ DisabledComponents=0xFF ＋ NIC バインド解除）、hosts エントリ登録、IP/DNS 現況の記録</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>computer_name / os_timezone / os_locale / eventlog_config / pagefile_configure</t>
+          <t>disable_ipv6 / hosts_entries</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>win_localuser</t>
+          <t>win_os_basic</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>1.3 ユーザアカウント / 6.ﾛｰｶﾙﾕｰｻﾞｰ / 7.ﾛｰｶﾙｸﾞﾙｰﾌﾟ</t>
+          <t>1.6 言語設定 / 3.ｻｰﾊﾞｰﾏﾈｰｼﾞｬｰ / 4.Windowsﾛｸﾞ(20480KB×3) / 5.ｼｽﾃﾑのﾌﾟﾛﾊﾟﾃｨ</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>ローカルユーザ作成、グループ所属、Guest 無効化。ファイルサーバは kansai / docways / NPJS</t>
+          <t>コンピュータ名、タイムゾーン、日本語ロケール、IE ESC 無効化、テレメトリ オフ、イベントログ最大サイズ、ページングファイル</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>local_users / disable_guest_account</t>
+          <t>computer_name / os_timezone / os_locale / eventlog_config / pagefile_configure</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>win_remote</t>
+          <t>win_localuser</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>1.7 リモート接続設定</t>
+          <t>1.3 ユーザアカウント / 6.ﾛｰｶﾙﾕｰｻﾞｰ / 7.ﾛｰｶﾙｸﾞﾙｰﾌﾟ</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>リモートデスクトップ許可、NLA 要求、WinRM(リモート管理)有効化</t>
+          <t>ローカルユーザ作成、グループ所属、Guest 無効化。ファイルサーバは kansai / docways / NPJS</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>enable_rdp / rdp_require_nla</t>
+          <t>local_users / disable_guest_account</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>win_security</t>
+          <t>win_remote</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>1.10 ファイアウォール / 1.11 Defender / 1.12 UAC / 13.UAC無効化 / 15.ローカルGPO</t>
+          <t>1.7 リモート接続設定</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ファイアウォール無効化＋ログ設定、Defender のポリシー無効化、UAC 無効化(EnableLUA=0 / luafv Start=4)</t>
+          <t>リモートデスクトップ許可、NLA 要求、WinRM(リモート管理)有効化</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>firewall_state / disable_defender_by_policy / disable_uac</t>
+          <t>enable_rdp / rdp_require_nla</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>win_features</t>
+          <t>win_security</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>1.9 役割と機能 / 12.役割と機能の追加</t>
+          <t>1.10 ファイアウォール / 1.11 Defender / 1.12 UAC / 13.UAC無効化 / 15.ローカルGPO</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>役割・機能の追加／削除、ベンダー様対応範囲の通知。ファイルサーバは IIS(Web/FTP) / ファイルサーバ / FSRM / ASP.NET 4.8 / RSAT(FSRM)</t>
+          <t>ファイアウォール無効化＋ログ設定、Defender のポリシー無効化、UAC 無効化(EnableLUA=0 / luafv Start=4)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>windows_features / windows_features_expected_default / windows_features_absent / vendor_scope_features</t>
+          <t>firewall_state / disable_defender_by_policy / disable_uac</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>win_services</t>
+          <t>win_features</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>1.15 サービス設定 / 16.ｻｰﾋﾞｽ一覧</t>
+          <t>1.9 役割と機能 / 12.役割と機能の追加</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>サービスのスタートアップの種類・状態設定（vmictimesync を無効化）</t>
+          <t>役割・機能の追加／削除、ベンダー様対応範囲の通知。ファイルサーバは IIS(Web/FTP) / ファイルサーバ / FSRM / ASP.NET 4.8 / RSAT(FSRM)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>windows_services_config</t>
+          <t>windows_features / windows_features_expected_default / windows_features_absent / vendor_scope_features</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>win_update</t>
+          <t>win_services</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>1.14 Windows 更新プログラム / 14.適用ﾊﾟｯﾁ一覧 / 15.ローカルGPO</t>
+          <t>1.15 サービス設定 / 16.ｻｰﾋﾞｽ一覧</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>更新プログラムの適用（繰り返し）、ローカル GPO「自動更新を構成する」無効化、適用済みパッチ一覧取得</t>
+          <t>サービスのスタートアップの種類・状態設定（vmictimesync を無効化）</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>apply_windows_update / windows_update_categories / disable_auto_update_policy</t>
+          <t>windows_services_config</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>win_domain</t>
+          <t>win_update</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>1.2 ドメイン参加</t>
+          <t>1.14 Windows 更新プログラム / 14.適用ﾊﾟｯﾁ一覧 / 15.ローカルGPO</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>DC 昇格（新規フォレスト / 追加 DC）、メンバーサーバのドメイン参加。ファイルサーバはメンバー参加のみ</t>
+          <t>更新プログラムの適用（繰り返し）、ローカル GPO「自動更新を構成する」無効化、適用済みパッチ一覧取得</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>ad_domain_name / ad_mode / domain_dns_servers</t>
+          <t>apply_windows_update / windows_update_categories / disable_auto_update_policy</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>win_ntp</t>
+          <t>win_domain</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>1.8 時刻同期設定</t>
+          <t>1.2 ドメイン参加</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>PDC は ntp.nict.jp,0x8 と手動同期、それ以外（ファイルサーバを含む）はドメイン階層から自動同期</t>
+          <t>DC 昇格（新規フォレスト / 追加 DC）、メンバーサーバのドメイン参加。ファイルサーバはメンバー参加のみ</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>is_pdc_emulator / ntp_servers</t>
+          <t>ad_domain_name / ad_mode / domain_dns_servers</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>win_tasks</t>
+          <t>win_ntp</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>1.13 タスクスケジューラ</t>
+          <t>1.8 時刻同期設定</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>スケジュールタスク 8 件の登録、実行プログラムの存在確認</t>
+          <t>PDC は ntp.nict.jp,0x8 と手動同期、それ以外（ファイルサーバを含む）はドメイン階層から自動同期</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>scheduled_tasks / vault_task_run_user</t>
+          <t>is_pdc_emulator / ntp_servers</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>win_ftp</t>
+          <t>win_tasks</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>1.16 FTP設定</t>
+          <t>1.13 タスクスケジューラ</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>FTP サイト作成（バインド / SSL / 基本認証 / 承認規則 / ログ）、物理パスの ACL 付与</t>
+          <t>スケジュールタスク 8 件の登録、実行プログラムの存在確認</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>ftp_sites / ftp_log_directory / ftp_log_rollover</t>
+          <t>scheduled_tasks / vault_task_run_user</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>win_ftp</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>1.16 FTP設定</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>FTP サイト作成（バインド / SSL / 基本認証 / 承認規則 / ログ）、物理パスの ACL 付与</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>ftp_sites / ftp_log_directory / ftp_log_rollover</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>win_verify</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>全般</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>設定値の収集、設計値との突合せ、証跡の回収</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>evidence_dir_remote / evidence_dir_local / verify_fail_on_mismatch</t>
         </is>
@@ -819,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -842,7 +864,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>適用範囲</t>
+          <t>区分</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -854,136 +876,51 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>inventory/group_vars/all/main.yml</t>
+          <t>roles/win_standard/defaults/main.yml</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>全ホスト</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>設計書「1.概要」の共通パラメータ</t>
+          <t>JBCC 標準値のうち、複数ロールから参照されるもの</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>inventory/group_vars/all/vault.yml</t>
+          <t>roles/&lt;ロール&gt;/defaults/main.yml</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>全ホスト</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>認証情報（ansible-vault で暗号化必須）</t>
+          <t>そのロールだけが使う標準値</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>inventory/group_vars/windows.yml</t>
+          <t>inventories/_template/</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Windows 全ホスト</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>WinRM 接続設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>inventory/group_vars/dc.yml</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>S-AZR-001/002</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>AD / DNS の役割、DC 昇格モード（旧設計書由来。現行設計書に AD シートは無い）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>inventory/group_vars/member.yml</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>S-AZR-003〜006</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>ローカルユーザ、ディスク構成</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>inventory/group_vars/fileserver.yml</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>S-AZR-007 / Ansible-TEST-FS</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>今回の設計対象。IIS・FTP・FSRM の役割、ローカルユーザ、イベントログ、FTP サイト、タスクスケジューラ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>inventory/host_vars/S-AZR-00N.yml</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>各ホスト</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>コンピュータ名、OS バージョン、用途、PDC 判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>inventory/host_vars/Ansible-TEST-FS/main.yml</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>検証機</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>今回の検証対象（ファイルサーバ相当）</t>
+          <t>新規案件のインベントリ雛形</t>
         </is>
       </c>
     </row>

--- a/docs/02_ロール一覧.xlsx
+++ b/docs/02_ロール一覧.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -767,64 +767,86 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>win_tasks</t>
+          <t>win_software</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>1.13 タスクスケジューラ</t>
+          <t>9.導入ｿﾌﾄｳｪｱ</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>スケジュールタスク 8 件の登録、実行プログラムの存在確認</t>
+          <t>ソフトウェアの導入（URL / パスのインストーラをサイレント実行）。「プログラムと機能」の表示名で導入済みを判定し、導入済みなら何もしない。入手先が未定のものは skip で対象外にする</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>scheduled_tasks / vault_task_run_user</t>
+          <t>software_packages</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>win_ftp</t>
+          <t>win_tasks</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>1.16 FTP設定</t>
+          <t>1.13 タスクスケジューラ</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>FTP サイト作成（バインド / SSL / 基本認証 / 承認規則 / ログ）、物理パスの ACL 付与</t>
+          <t>スケジュールタスク 8 件の登録、実行プログラムの存在確認</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>ftp_sites / ftp_log_directory / ftp_log_rollover</t>
+          <t>scheduled_tasks / vault_task_run_user</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>win_ftp</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>1.16 FTP設定</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>FTP サイト作成（バインド / SSL / 基本認証 / 承認規則 / ログ）、物理パスの ACL 付与</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>ftp_sites / ftp_log_directory / ftp_log_rollover</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>win_verify</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>全般</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>設定値の収集、設計値との突合せ、証跡の回収</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>evidence_dir_remote / evidence_dir_local / verify_fail_on_mismatch</t>
         </is>
